--- a/survey_templates/035_fetish_interest_survey--survey_templates.xlsx
+++ b/survey_templates/035_fetish_interest_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -873,12 +873,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>fetus_interest</t>
+          <t>fetus_interest_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fetish Interest</t>
+          <t>Fetus Interest 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fetish Boundary</t>
+          <t>Fetus Boundary</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Other Boundary</t>
+          <t>Other Fetish Boundary</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -973,12 +973,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>fetish_interest_level</t>
+          <t>fetish_interest_level_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Interest Level</t>
+          <t>Fetish Interest Level 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -996,12 +996,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>other_fetish_interest_level</t>
+          <t>other_fetish_interest_level_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Other Interest Level</t>
+          <t>Other Fetish Interest Level 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Note 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>date_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Date 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1117,7 +1117,7 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1210,7 +1210,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>fetus_interest_choices</t>
+          <t>fetus_interest_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1227,7 +1227,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>fetus_interest_choices</t>
+          <t>fetus_interest_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
